--- a/Irish Football Pyramid.xlsx
+++ b/Irish Football Pyramid.xlsx
@@ -8,17 +8,38 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marzu\FM Irish Football\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="275" documentId="8_{65CE589B-2F4C-477E-8FF6-6193AEA0A127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94F0AB35-C218-4909-A640-A274174509E0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A52E75-C179-437A-8F29-7BB0412EA634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{A69142AE-CDDD-4111-B852-50CA28413CE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="1000" firstSheet="8" activeTab="18" xr2:uid="{ED595454-472F-41A8-9BCD-2CE132AA83CF}"/>
   </bookViews>
   <sheets>
-    <sheet name="Home" sheetId="1" r:id="rId1"/>
-    <sheet name="Premier Division" sheetId="2" r:id="rId2"/>
-    <sheet name="First Division" sheetId="3" r:id="rId3"/>
-    <sheet name="National League" sheetId="6" r:id="rId4"/>
-    <sheet name="LSL" sheetId="4" r:id="rId5"/>
-    <sheet name="MSL" sheetId="5" r:id="rId6"/>
+    <sheet name="Notes" sheetId="7" r:id="rId1"/>
+    <sheet name="Home" sheetId="1" r:id="rId2"/>
+    <sheet name="Premier Division" sheetId="2" r:id="rId3"/>
+    <sheet name="First Division" sheetId="3" r:id="rId4"/>
+    <sheet name="National League" sheetId="6" r:id="rId5"/>
+    <sheet name="LSL" sheetId="4" r:id="rId6"/>
+    <sheet name="Senior Sunday" sheetId="56" r:id="rId7"/>
+    <sheet name="Senior 1 Sunday" sheetId="55" r:id="rId8"/>
+    <sheet name="Senior 1A Sunday" sheetId="54" r:id="rId9"/>
+    <sheet name="Senior 1B Sunday" sheetId="53" r:id="rId10"/>
+    <sheet name="Major Sunday" sheetId="51" r:id="rId11"/>
+    <sheet name="Major 1 Sunday" sheetId="52" r:id="rId12"/>
+    <sheet name="Premier Sunday" sheetId="47" r:id="rId13"/>
+    <sheet name="Premier 1 Sunday" sheetId="46" r:id="rId14"/>
+    <sheet name="Division 3 Sunday" sheetId="50" r:id="rId15"/>
+    <sheet name="Division 3A Sunday" sheetId="49" r:id="rId16"/>
+    <sheet name="U19" sheetId="48" r:id="rId17"/>
+    <sheet name="MSL" sheetId="5" r:id="rId18"/>
+    <sheet name="Senior Premier Division" sheetId="45" r:id="rId19"/>
+    <sheet name="Senior First Division" sheetId="44" r:id="rId20"/>
+    <sheet name="Senior Second Division" sheetId="43" r:id="rId21"/>
+    <sheet name="Junior Premier Division" sheetId="42" r:id="rId22"/>
+    <sheet name="Junior First Division" sheetId="57" r:id="rId23"/>
+    <sheet name="Junior Second Division" sheetId="41" r:id="rId24"/>
+    <sheet name="Junior Third Division" sheetId="58" r:id="rId25"/>
+    <sheet name="Junior Fourth Division" sheetId="59" r:id="rId26"/>
+    <sheet name="Floodlit League" sheetId="40" r:id="rId27"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +69,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="10">
+  <futureMetadata name="XLRICHVALUE" count="29">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -119,8 +140,141 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="10"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="11"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="13"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="14"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="15"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="16"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="17"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="18"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="19"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="20"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="21"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="22"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="23"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="24"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="25"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="26"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="27"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="28"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="10">
+  <valueMetadata count="29">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -150,13 +304,70 @@
     </bk>
     <bk>
       <rc t="1" v="9"/>
+    </bk>
+    <bk>
+      <rc t="1" v="10"/>
+    </bk>
+    <bk>
+      <rc t="1" v="11"/>
+    </bk>
+    <bk>
+      <rc t="1" v="12"/>
+    </bk>
+    <bk>
+      <rc t="1" v="13"/>
+    </bk>
+    <bk>
+      <rc t="1" v="14"/>
+    </bk>
+    <bk>
+      <rc t="1" v="15"/>
+    </bk>
+    <bk>
+      <rc t="1" v="16"/>
+    </bk>
+    <bk>
+      <rc t="1" v="17"/>
+    </bk>
+    <bk>
+      <rc t="1" v="18"/>
+    </bk>
+    <bk>
+      <rc t="1" v="19"/>
+    </bk>
+    <bk>
+      <rc t="1" v="20"/>
+    </bk>
+    <bk>
+      <rc t="1" v="21"/>
+    </bk>
+    <bk>
+      <rc t="1" v="22"/>
+    </bk>
+    <bk>
+      <rc t="1" v="23"/>
+    </bk>
+    <bk>
+      <rc t="1" v="24"/>
+    </bk>
+    <bk>
+      <rc t="1" v="25"/>
+    </bk>
+    <bk>
+      <rc t="1" v="26"/>
+    </bk>
+    <bk>
+      <rc t="1" v="27"/>
+    </bk>
+    <bk>
+      <rc t="1" v="28"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="102">
   <si>
     <t>Premier Divison</t>
   </si>
@@ -207,6 +418,261 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Group 1</t>
+  </si>
+  <si>
+    <t>Group 2</t>
+  </si>
+  <si>
+    <t>Group 3</t>
+  </si>
+  <si>
+    <t>26/27  Season</t>
+  </si>
+  <si>
+    <t>27/28  Season Onwards</t>
+  </si>
+  <si>
+    <t>National League North</t>
+  </si>
+  <si>
+    <t>National League South</t>
+  </si>
+  <si>
+    <t>*Predicted*</t>
+  </si>
+  <si>
+    <t>Bonagee United</t>
+  </si>
+  <si>
+    <t>Cockhill Celtic</t>
+  </si>
+  <si>
+    <t>Home Farm</t>
+  </si>
+  <si>
+    <t>Lucan United</t>
+  </si>
+  <si>
+    <t>Mervue United</t>
+  </si>
+  <si>
+    <t>Mayo FC</t>
+  </si>
+  <si>
+    <t>Salthill Devon</t>
+  </si>
+  <si>
+    <t>TU Dublin</t>
+  </si>
+  <si>
+    <t>St Francis</t>
+  </si>
+  <si>
+    <t>CK United</t>
+  </si>
+  <si>
+    <t>Killarney Celtic</t>
+  </si>
+  <si>
+    <t>Newbridge Town</t>
+  </si>
+  <si>
+    <t>UCC</t>
+  </si>
+  <si>
+    <t>Villa</t>
+  </si>
+  <si>
+    <t>Lucan United badge</t>
+  </si>
+  <si>
+    <t>Letterkenny badge</t>
+  </si>
+  <si>
+    <t>Problems</t>
+  </si>
+  <si>
+    <t>Ideas</t>
+  </si>
+  <si>
+    <t>Website of badges</t>
+  </si>
+  <si>
+    <t>Salthill Devon crest</t>
+  </si>
+  <si>
+    <t>Tu Dublin Crest</t>
+  </si>
+  <si>
+    <t>Killarney Crest</t>
+  </si>
+  <si>
+    <t>Letterkenny Rovers</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Senior Sunday</t>
+  </si>
+  <si>
+    <t>Senior 1 Sunday</t>
+  </si>
+  <si>
+    <t>Senior 1A Sunday</t>
+  </si>
+  <si>
+    <t>Senior 1B Sunday</t>
+  </si>
+  <si>
+    <t>Major Sunday</t>
+  </si>
+  <si>
+    <t>Major 1 Sunday</t>
+  </si>
+  <si>
+    <t>Premier Sunday</t>
+  </si>
+  <si>
+    <t>Premier 1 Sunday</t>
+  </si>
+  <si>
+    <t>Division 3 Sunday</t>
+  </si>
+  <si>
+    <t>Division 3A Sunday</t>
+  </si>
+  <si>
+    <t>U19</t>
+  </si>
+  <si>
+    <t>Major Saturday</t>
+  </si>
+  <si>
+    <t>Major 1 Saturday</t>
+  </si>
+  <si>
+    <t>Major 1A Saturday</t>
+  </si>
+  <si>
+    <t>Major 1B Saturday</t>
+  </si>
+  <si>
+    <t>Major 1C Saturday</t>
+  </si>
+  <si>
+    <t>Major 1D Saturday</t>
+  </si>
+  <si>
+    <t>Premier Saturday</t>
+  </si>
+  <si>
+    <t>Premier 1 Saturday</t>
+  </si>
+  <si>
+    <t>Division 3 Saturday</t>
+  </si>
+  <si>
+    <t>Division 3A Saturday</t>
+  </si>
+  <si>
+    <t>Division 3B Saturday</t>
+  </si>
+  <si>
+    <t>Division 3C Saturday</t>
+  </si>
+  <si>
+    <t>Senior Premier Division</t>
+  </si>
+  <si>
+    <t>Senior First Division</t>
+  </si>
+  <si>
+    <t>Senior Second Division</t>
+  </si>
+  <si>
+    <t>Junior Premier Division</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Junior First Division</t>
+  </si>
+  <si>
+    <t>Junior Second Division</t>
+  </si>
+  <si>
+    <t>Junior Third Division</t>
+  </si>
+  <si>
+    <t>Junior Fourth Division</t>
+  </si>
+  <si>
+    <t>Floodlit League</t>
+  </si>
+  <si>
+    <t>Carrigaline United</t>
+  </si>
+  <si>
+    <t>Mayfield United</t>
+  </si>
+  <si>
+    <t>Douglas Hall</t>
+  </si>
+  <si>
+    <t>Blarney United</t>
+  </si>
+  <si>
+    <t>Midleton</t>
+  </si>
+  <si>
+    <t>College Corinthians</t>
+  </si>
+  <si>
+    <t>Rockmount</t>
+  </si>
+  <si>
+    <t>Castleview</t>
+  </si>
+  <si>
+    <t>St Marys</t>
+  </si>
+  <si>
+    <t>Ringmahon Rangers</t>
   </si>
 </sst>
 </file>
@@ -294,7 +760,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -349,34 +815,114 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color theme="1"/>
       </left>
       <right/>
-      <top style="medium">
+      <top style="thin">
         <color theme="1"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color theme="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
         <color theme="1"/>
       </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
+      <top/>
+      <bottom style="thin">
         <color theme="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
         <color theme="1"/>
@@ -390,11 +936,9 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
+      <left/>
       <right style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
         <color theme="1"/>
@@ -406,7 +950,7 @@
     </border>
     <border>
       <left style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
         <color theme="1"/>
@@ -415,169 +959,7 @@
         <color theme="1"/>
       </top>
       <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -590,14 +972,81 @@
         <color theme="1"/>
       </top>
       <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom style="thin">
@@ -606,35 +1055,282 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color theme="1"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -643,33 +1339,7 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -677,7 +1347,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -689,124 +1359,237 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -878,7 +1661,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="29">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -919,6 +1702,82 @@
     <v>9</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>10</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>11</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>12</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>13</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>14</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>15</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>16</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>17</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>18</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>19</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>20</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>21</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>22</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>23</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>24</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>25</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>26</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>27</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>28</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -943,6 +1802,25 @@
   <rel r:id="rId8"/>
   <rel r:id="rId9"/>
   <rel r:id="rId10"/>
+  <rel r:id="rId11"/>
+  <rel r:id="rId12"/>
+  <rel r:id="rId13"/>
+  <rel r:id="rId14"/>
+  <rel r:id="rId15"/>
+  <rel r:id="rId16"/>
+  <rel r:id="rId17"/>
+  <rel r:id="rId18"/>
+  <rel r:id="rId19"/>
+  <rel r:id="rId20"/>
+  <rel r:id="rId21"/>
+  <rel r:id="rId22"/>
+  <rel r:id="rId23"/>
+  <rel r:id="rId24"/>
+  <rel r:id="rId25"/>
+  <rel r:id="rId26"/>
+  <rel r:id="rId27"/>
+  <rel r:id="rId28"/>
+  <rel r:id="rId29"/>
 </richValueRels>
 </file>
 
@@ -1262,7 +2140,518 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3582B53-9FAC-42CD-9861-2E007F5D07BA}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <f>ROW()-1</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <f>A2+1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <f t="shared" ref="A4:A9" si="0">A3+1</f>
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F5E24F0-55A3-4881-80F6-CA904EBC98C1}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1:C1" location="Home!A1" display="Home" xr:uid="{02AAA7F8-52F4-421E-8362-4CD6A28007F7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{311A2CA0-0E50-4B70-A29D-5A70BAC1FE0D}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1:C1" location="Home!A1" display="Home" xr:uid="{563C33B0-9E3B-4E5B-8D6D-E1BF7B7FFB99}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2CDCBC-69C0-4017-8A55-6B4A9A8E151B}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1:C1" location="Home!A1" display="Home" xr:uid="{800590D4-9B41-4A14-A143-795CC299A6C0}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5452E66D-AFC2-4A0F-8EF1-B3A92D595B76}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1:C1" location="Home!A1" display="Home" xr:uid="{1A6E5B46-712A-4D85-82DD-C6F1FA1AF8CA}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ADB1CF1-8523-4843-BDB8-B9D757A77949}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1:C1" location="Home!A1" display="Home" xr:uid="{B61FDFCA-A922-479F-9DF3-675B31DB02F3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1013BFA4-875B-40F8-8525-1F72A976F09A}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1:C1" location="Home!A1" display="Home" xr:uid="{FE523E51-70FC-41CC-AC18-9EFA8162256A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28311DCF-E872-4765-858C-D0504E5E8AF8}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1:C1" location="Home!A1" display="Home" xr:uid="{7DAC0F57-5825-41A3-9F14-4C7C68FD0CD2}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AE85CC0-3BE6-4886-8CF7-1D51D42C8A7C}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1:C1" location="Home!A1" display="Home" xr:uid="{AA3FE423-AD41-4574-910A-24117CFA52B8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C5932EB-0701-4CF8-BA7F-63C4ADC0E20B}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="64" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="68" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="68" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="68" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="70" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="68" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="68" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="68" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="68" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="73" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Home!A1" display="Home" xr:uid="{3F2089E0-957E-4252-AEB4-CCEE53D0B9DA}"/>
+    <hyperlink ref="A5" location="'Senior First Division'!A1" display="Senior First Division" xr:uid="{F1C1A61A-F7A0-4284-BD83-D76AD6A3C934}"/>
+    <hyperlink ref="A4" location="'Senior Premier Division'!A1" display="Senior Premier Division" xr:uid="{F94D00D6-EA7C-4A83-BCD3-43C970B45E59}"/>
+    <hyperlink ref="A6" location="'Senior Second Division'!A1" display="Senior Second Division" xr:uid="{2CDFD977-5B67-4951-B175-A674C28AB46B}"/>
+    <hyperlink ref="A7" location="'Junior Premier Division'!A1" display="Junior Premier Division" xr:uid="{FEF38305-34E1-4B09-9E40-ED6259758823}"/>
+    <hyperlink ref="A8" location="'Junior First Division'!A1" display=" Junior First Division" xr:uid="{71CA886D-BDA4-4267-8A46-4F987C3B6796}"/>
+    <hyperlink ref="A9" location="'Junior Second Division'!A1" display="Junior Second Division" xr:uid="{E2158FF0-E077-4521-A9C7-680C411697C6}"/>
+    <hyperlink ref="A10" location="'Junior Third Division'!A1" display="Junior Third Division" xr:uid="{F6A71FBA-67CC-47A1-A694-D248C552E450}"/>
+    <hyperlink ref="A11" location="'Junior Fourth Division'!A1" display="Junior Fourth Division" xr:uid="{ACABCF91-4300-4B6A-9B5E-19174F5B42C7}"/>
+    <hyperlink ref="A12" location="'Floodlit League'!A1" display="Floodlit League" xr:uid="{605FC549-AC5D-4BD1-8017-22AF6F71BCDB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF565F74-09D1-4ABF-8584-029ACF79A07D}">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="2.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26" style="79" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="84"/>
+      <c r="C1" s="85" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="39"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="28"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="74" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="28"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="82">
+        <f>ROW()-3</f>
+        <v>1</v>
+      </c>
+      <c r="B4" s="38"/>
+      <c r="C4" s="76" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="81">
+        <f>A4+1</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="47"/>
+      <c r="C5" s="77" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="80">
+        <f t="shared" ref="A6:A13" si="0">A5+1</f>
+        <v>3</v>
+      </c>
+      <c r="B6" s="83"/>
+      <c r="C6" s="77" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="81">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="77" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="80">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="83"/>
+      <c r="C8" s="77" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="80">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="83"/>
+      <c r="C9" s="77" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="80">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="83"/>
+      <c r="C10" s="77" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="81">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B11" s="47"/>
+      <c r="C11" s="77" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="81">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B12" s="47"/>
+      <c r="C12" s="77" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="54">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="78" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F14" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C1" location="MSL!A1" display="MSL" xr:uid="{4BEC0F56-3A61-4272-9519-92D3ACC19D22}"/>
+    <hyperlink ref="A1" location="Home!A1" display="Home" xr:uid="{EFA5A242-2D15-426A-A563-0917B9BC68E2}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12F4F16E-8057-48CD-BE30-DEFB4230A248}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1271,32 +2660,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="18"/>
+      <c r="B1" s="13"/>
     </row>
     <row r="2" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
     </row>
     <row r="3" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="25"/>
+      <c r="B3" s="16"/>
     </row>
     <row r="4" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="27"/>
+      <c r="B4" s="18"/>
     </row>
     <row r="5" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="29"/>
+      <c r="B5" s="20"/>
     </row>
     <row r="6" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -1323,427 +2712,1305 @@
     <hyperlink ref="A1:B1" location="Home!A1" display="Home" xr:uid="{CD616329-B7F8-4BF3-93B2-645504D9946A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A478345-36D2-4AB6-B3A4-BA14A036FD7F}">
-  <dimension ref="A1:F13"/>
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3DE1F5-B6FF-4301-BD55-E0D0790AEFB5}">
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="2.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="32"/>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="35"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <f>ROW()-3</f>
-        <v>1</v>
-      </c>
-      <c r="B4" s="9" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="38"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <f t="shared" ref="A5:A13" si="0">ROW()-3</f>
-        <v>2</v>
-      </c>
-      <c r="B5" s="8" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="23"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="B6" s="8" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="23"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B7" s="8" t="e" vm="4">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="23"/>
-      <c r="F7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <f t="shared" si="0"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1:C1" location="Home!A1" display="Home" xr:uid="{574B702C-096F-4930-A374-FE8EF0D97E47}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E875B901-6467-46E8-98C1-C3D3003763E9}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="8" t="e" vm="5">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="23"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B9" s="8" t="e" vm="6">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="23"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B10" s="8" t="e" vm="7">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="23"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B11" s="8" t="e" vm="8">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="23"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B12" s="8" t="e" vm="9">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="23"/>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B13" s="10" t="e" vm="10">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="12"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:D13">
-    <sortCondition ref="C4:C13"/>
-  </sortState>
-  <mergeCells count="13">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1:C1" location="Home!A1" display="Home" xr:uid="{6C629C35-24BD-4E2C-A5D7-3AC79BF1900F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2647C294-2CF8-4C7D-A622-FCE4C58604DC}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1:C1" location="Home!A1" display="Home" xr:uid="{786B9E7B-AF39-4592-946C-F586653E8EDA}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F17D5507-DB81-42E1-B78E-86A35049944E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{900782BE-FE79-412C-8141-8516F66C9EAA}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1:C1" location="Home!A1" display="Home" xr:uid="{8F8F4FBA-08EB-4BA7-8590-F2F2810A6EF3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55241D52-93BF-4D7E-BFB0-9411F8353A02}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D25292A-B588-4594-94F9-ACC9473509D6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4582A08-C65E-456A-8226-0E0DE106FF3B}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1:C1" location="Home!A1" display="Home" xr:uid="{985EFA15-CF06-4E47-BF02-A4DF583AABEF}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A478345-36D2-4AB6-B3A4-BA14A036FD7F}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="2.7109375" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="32"/>
+      <c r="C3" s="33"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="23">
+        <f>ROW()-3</f>
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="24">
+        <f t="shared" ref="A5:A13" si="0">ROW()-3</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="5" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B6" s="5" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="24">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="24">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="5" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="24">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="5" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="24">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="24">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B11" s="5" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="24">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B12" s="5" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="25">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B13" s="26" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:C13">
+    <sortCondition ref="C4:C13"/>
+  </sortState>
+  <mergeCells count="3">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:C3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1:C1" location="Home!A1" display="Home" xr:uid="{37E2BB52-0CFF-4407-8DC9-A2D541DD4AEF}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A63847B3-5E54-4727-A965-0736AC5BCC9A}">
-  <dimension ref="A1:D13"/>
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="18"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="15"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="B3" s="9"/>
+      <c r="C3" s="10"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="23">
         <f>ROW()-3</f>
         <v>1</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="21"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="B4" s="6" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="23">
         <f t="shared" ref="A5:A13" si="0">ROW()-3</f>
         <v>2</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="23"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="B5" s="5" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="28"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="23">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="23"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+      <c r="B6" s="5" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="23">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="23"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+      <c r="B7" s="5" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="23"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
+      <c r="B8" s="5" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="28"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="23">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
+      <c r="B9" s="5" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="23">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="23"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
+      <c r="B10" s="5" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="23">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="23"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
+      <c r="B11" s="5" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="23">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="23"/>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6">
+      <c r="B12" s="5" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="48">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="12"/>
+      <c r="B13" s="26" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C5:C13">
+    <sortCondition ref="C4:C13"/>
+  </sortState>
+  <mergeCells count="3">
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1:B1" location="Home!A1" display="Home" xr:uid="{60F5A6BF-F013-45FE-A9D1-79B863726772}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22B485B3-27ED-41C6-A812-BBCCAA1FDEDD}">
-  <dimension ref="A1:J22"/>
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="B1:T33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="2.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="7" max="7" width="2.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" customWidth="1"/>
+    <col min="12" max="12" width="17.5703125" customWidth="1"/>
+    <col min="15" max="15" width="2.7109375" customWidth="1"/>
+    <col min="16" max="16" width="17.5703125" customWidth="1"/>
+    <col min="19" max="19" width="2.7109375" customWidth="1"/>
+    <col min="20" max="20" width="17.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+    </row>
+    <row r="2" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="13"/>
+      <c r="N2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="13"/>
+    </row>
+    <row r="3" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+    </row>
+    <row r="4" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="13"/>
+      <c r="N4" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="12"/>
+      <c r="T4" s="13"/>
+    </row>
+    <row r="5" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
+      <c r="P5" s="35"/>
+      <c r="Q5" s="35"/>
+      <c r="R5" s="35"/>
+      <c r="S5" s="35"/>
+      <c r="T5" s="35"/>
+    </row>
+    <row r="6" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="22"/>
+      <c r="N6" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="40"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="40"/>
+    </row>
+    <row r="7" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="37"/>
+      <c r="S7" s="37"/>
+      <c r="T7" s="37"/>
+    </row>
+    <row r="8" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="45"/>
+      <c r="D8" s="46"/>
+      <c r="F8" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
+      <c r="J8" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="45"/>
+      <c r="L8" s="46"/>
+      <c r="N8" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="O8" s="45"/>
+      <c r="P8" s="45"/>
+      <c r="Q8" s="45"/>
+      <c r="R8" s="45"/>
+      <c r="S8" s="45"/>
+      <c r="T8" s="46"/>
+    </row>
+    <row r="9" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="23">
+        <f>ROW()-8</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="23">
+        <f>ROW()-8</f>
+        <v>1</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="23">
+        <f>ROW()-8</f>
+        <v>1</v>
+      </c>
+      <c r="K9" s="6" t="e" vm="22">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L9" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="N9" s="35"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="35"/>
+      <c r="S9" s="35"/>
+      <c r="T9" s="35"/>
+    </row>
+    <row r="10" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="23">
+        <f t="shared" ref="B10:B13" si="0">ROW()-8</f>
+        <v>2</v>
+      </c>
+      <c r="C10" s="5" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="23">
+        <f t="shared" ref="F10:F13" si="1">ROW()-8</f>
+        <v>2</v>
+      </c>
+      <c r="G10" s="5" t="e" vm="24">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="J10" s="23">
+        <f t="shared" ref="J10:J13" si="2">ROW()-8</f>
+        <v>2</v>
+      </c>
+      <c r="K10" s="5"/>
+      <c r="L10" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="N10" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="O10" s="45"/>
+      <c r="P10" s="46"/>
+      <c r="R10" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="S10" s="45"/>
+      <c r="T10" s="46"/>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B11" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C11" s="5" t="e" vm="25">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="23">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="23">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="K11" s="5" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L11" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="N11" s="53">
+        <f>ROW()-10</f>
+        <v>1</v>
+      </c>
+      <c r="O11" s="6" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P11" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="R11" s="53">
+        <f>ROW()-10</f>
+        <v>1</v>
+      </c>
+      <c r="S11" s="6" t="e" vm="22">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T11" s="43" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B12" s="23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="23">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="G12" s="5" t="e" vm="27">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H12" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" s="23">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="K12" s="5"/>
+      <c r="L12" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="N12" s="53">
+        <f t="shared" ref="N12:N20" si="3">ROW()-10</f>
+        <v>2</v>
+      </c>
+      <c r="O12" s="5" t="e" vm="24">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P12" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="R12" s="53">
+        <f t="shared" ref="R12:R20" si="4">ROW()-10</f>
+        <v>2</v>
+      </c>
+      <c r="S12" s="5"/>
+      <c r="T12" s="27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="48">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C13" s="26" t="e" vm="28">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="48">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="G13" s="26"/>
+      <c r="H13" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" s="48">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="K13" s="26" t="e" vm="29">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L13" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="N13" s="53">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="O13" s="5" t="e" vm="28">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P13" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="R13" s="53">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="S13" s="5" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T13" s="27" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="N14" s="53">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="O14" s="5" t="e" vm="25">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P14" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="R14" s="53">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="S14" s="5"/>
+      <c r="T14" s="27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="N15" s="53">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="O15" s="56" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P15" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="R15" s="53">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="S15" s="56" t="e" vm="29">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T15" s="55" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="N16" s="53">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="O16" s="57"/>
+      <c r="P16" s="58"/>
+      <c r="R16" s="53">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="S16" s="5" t="e" vm="27">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T16" s="50" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="12:20" x14ac:dyDescent="0.25">
+      <c r="N17" s="53">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="O17" s="5"/>
+      <c r="P17" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="R17" s="53">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="S17" s="49"/>
+      <c r="T17" s="50" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="12:20" x14ac:dyDescent="0.25">
+      <c r="N18" s="53">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="O18" s="5"/>
+      <c r="P18" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="R18" s="53">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="S18" s="49"/>
+      <c r="T18" s="50"/>
+    </row>
+    <row r="19" spans="12:20" x14ac:dyDescent="0.25">
+      <c r="N19" s="53">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="P19" s="27"/>
+      <c r="R19" s="53">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="S19" s="49"/>
+      <c r="T19" s="50"/>
+    </row>
+    <row r="20" spans="12:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N20" s="54">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="O20" s="26"/>
+      <c r="P20" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="R20" s="54">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="S20" s="51"/>
+      <c r="T20" s="52"/>
+    </row>
+    <row r="25" spans="12:20" x14ac:dyDescent="0.25">
+      <c r="L25" s="4"/>
+    </row>
+    <row r="33" spans="19:19" x14ac:dyDescent="0.25">
+      <c r="S33" s="28"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="O12:P20">
+    <sortCondition descending="1" ref="O11:O20"/>
+  </sortState>
+  <mergeCells count="21">
+    <mergeCell ref="N3:T3"/>
+    <mergeCell ref="N8:T8"/>
+    <mergeCell ref="N7:T7"/>
+    <mergeCell ref="N9:T9"/>
+    <mergeCell ref="N1:T1"/>
+    <mergeCell ref="N4:T4"/>
+    <mergeCell ref="N5:T5"/>
+    <mergeCell ref="N6:T6"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="B6:L6"/>
+    <mergeCell ref="N2:T2"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B7:L7"/>
+    <mergeCell ref="B5:L5"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B1:L1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="N2:P2" location="Home!A1" display="Home" xr:uid="{8A56A6D3-C030-4346-89D1-386541130501}"/>
+    <hyperlink ref="B2:L2" location="Home!A1" display="Home" xr:uid="{7FACE44E-5BC4-4929-BABC-F46EF862513B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{679F141F-FB0D-4C6B-84E7-F2E4A11C4118}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="26" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="13"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="60"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="66" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="67" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="68" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="62" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="69" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="62" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="62" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="70" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="62" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="28"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="65" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="70" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="62" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="68" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="65" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="70" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="62" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="28"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="62" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="71" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="28"/>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="72"/>
+      <c r="D16" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B5" location="'Senior Sunday'!A1" display="Senior Sunday" xr:uid="{51EC4AB9-B7D9-42DE-A672-0978FD00CC88}"/>
+    <hyperlink ref="B6" location="'Senior 1 Sunday'!A1" display="Senior 1 Sunday" xr:uid="{016B1364-E236-4940-9680-2BBF666728CF}"/>
+    <hyperlink ref="B7" location="'Senior 1A Sunday'!A1" display="Senior 1A Sunday" xr:uid="{EAA8CA33-DC73-4703-9D0C-79E0DEA00FEB}"/>
+    <hyperlink ref="B8" location="'Senior 1B Sunday'!A1" display="Senior 1B Sunday" xr:uid="{09A47DA1-6D6D-4F9F-8BF8-BB9B7CBA602D}"/>
+    <hyperlink ref="B9" location="'Major Sunday'!A1" display="Major Sunday" xr:uid="{A7A64453-1E1B-48A5-914F-D0B79BB9EF7C}"/>
+    <hyperlink ref="B10" location="'Major 1 Sunday'!A1" display="Major 1 Sunday" xr:uid="{63DC165B-1248-4173-8771-C4B623ECC5EF}"/>
+    <hyperlink ref="B11" location="'Premier Sunday'!A1" display="Premier Sunday" xr:uid="{BFFF77B1-E161-4139-9ACC-8C34310276BB}"/>
+    <hyperlink ref="B12" location="'Premier 1 Sunday'!A1" display="Premier 1 Sunday" xr:uid="{3CDE1AE8-0C71-41BA-92F6-25654406880B}"/>
+    <hyperlink ref="B13" location="'Division 3 Sunday'!A1" display="Division 3 Sunday" xr:uid="{25420B56-BC74-4976-8276-92C58D78342B}"/>
+    <hyperlink ref="B14" location="'Division 3A Sunday'!A1" display="Division 3A Sunday" xr:uid="{2F0F8B11-6A00-4508-B76B-F740EA56A7FA}"/>
+    <hyperlink ref="B15:B16" location="'U19'!A1" display="U19" xr:uid="{12245DAC-A060-42D4-9353-DEFD59E395B0}"/>
+    <hyperlink ref="A1:B1" location="Home!A1" display="Home" xr:uid="{F47B0A28-7CCA-40BC-8EC4-9FFF0FC5AB30}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE17647E-6D44-40E4-B97F-71306066FC8C}">
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="18"/>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="39" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="40"/>
-    </row>
-    <row r="22" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J22" s="4"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A3:B3"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A1:B1" location="Home!A1" display="Home" xr:uid="{8A56A6D3-C030-4346-89D1-386541130501}"/>
+    <hyperlink ref="A1:C1" location="Home!A1" display="Home" xr:uid="{F221C042-9D16-44BD-A6EE-E91E2C61B454}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{679F141F-FB0D-4C6B-84E7-F2E4A11C4118}">
-  <dimension ref="A1:B3"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18663DAA-807B-4AF4-A3B5-4FD3C70CD5ED}">
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="18"/>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="42"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A3:B3"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A1:B1" location="Home!A1" display="Home" xr:uid="{2F3BBFDD-C986-40D5-A00B-443FA4EDAFC8}"/>
+    <hyperlink ref="A1:C1" location="Home!A1" display="Home" xr:uid="{1F1DF91D-0CEE-41B0-9A96-6F575BE4FBC5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C5932EB-0701-4CF8-BA7F-63C4ADC0E20B}">
-  <dimension ref="A1:B3"/>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4AC7A0B-A47D-4235-A968-9890E7585D8C}">
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="18"/>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="44"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A3:B3"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A1:B1" location="Home!A1" display="Home" xr:uid="{3F2089E0-957E-4252-AEB4-CCEE53D0B9DA}"/>
+    <hyperlink ref="A1:C1" location="Home!A1" display="Home" xr:uid="{75A02D7B-9117-4B78-8AB4-7D5D0B37F7BA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
